--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9884,0.0012,0.0092,0.0004</t>
-  </si>
-  <si>
-    <t>0.9674,0.0027,0.0091,0.0043</t>
-  </si>
-  <si>
-    <t>0.9848,0.0022,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.9629,0.0059,0.0178,0.0024</t>
-  </si>
-  <si>
-    <t>0.9914,0.0020,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9829,0.0025,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.9878,0.0029,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.9943,0.0006,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9813,0.0040,0.0021,0.0024</t>
-  </si>
-  <si>
-    <t>0.9865,0.0042,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.9800,0.0061,0.0042,0.0021</t>
-  </si>
-  <si>
-    <t>0.9907,0.0015,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.9791,0.0031,0.0277,0.0004</t>
-  </si>
-  <si>
-    <t>0.7085,0.0255,0.3662,0.0024</t>
-  </si>
-  <si>
-    <t>0.9755,0.0021,0.0408,0.0005</t>
-  </si>
-  <si>
-    <t>0.9706,0.0034,0.0398,0.0003</t>
-  </si>
-  <si>
-    <t>0.9364,0.0166,0.0489,0.0009</t>
-  </si>
-  <si>
-    <t>0.8054,0.1907,0.0251,0.0014</t>
-  </si>
-  <si>
-    <t>0.9524,0.0347,0.0103,0.0012</t>
-  </si>
-  <si>
-    <t>0.9794,0.0065,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.9512,0.0239,0.0157,0.0009</t>
-  </si>
-  <si>
-    <t>0.8408,0.1243,0.0412,0.0037</t>
-  </si>
-  <si>
-    <t>0.9645,0.0043,0.0452,0.0005</t>
-  </si>
-  <si>
-    <t>0.9784,0.0030,0.0230,0.0003</t>
-  </si>
-  <si>
-    <t>0.9312,0.0043,0.1306,0.0007</t>
-  </si>
-  <si>
-    <t>0.7712,0.0134,0.3024,0.0020</t>
-  </si>
-  <si>
-    <t>0.7100,0.0269,0.3010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9109,0.0030,0.1938,0.0003</t>
-  </si>
-  <si>
-    <t>0.7520,0.0047,0.4278,0.0006</t>
-  </si>
-  <si>
-    <t>0.9701,0.0101,0.0127,0.0007</t>
-  </si>
-  <si>
-    <t>0.9685,0.0079,0.0306,0.0012</t>
-  </si>
-  <si>
-    <t>0.1108,0.0081,0.9587,0.0007</t>
-  </si>
-  <si>
-    <t>0.9339,0.0215,0.0408,0.0007</t>
-  </si>
-  <si>
-    <t>0.9586,0.0170,0.0207,0.0013</t>
-  </si>
-  <si>
-    <t>0.9765,0.0098,0.0073,0.0004</t>
-  </si>
-  <si>
-    <t>0.9506,0.0301,0.0091,0.0022</t>
-  </si>
-  <si>
-    <t>0.8979,0.0535,0.0486,0.0048</t>
-  </si>
-  <si>
-    <t>0.8063,0.0042,0.3500,0.0001</t>
-  </si>
-  <si>
-    <t>0.5132,0.0015,0.7444,0.0004</t>
-  </si>
-  <si>
-    <t>0.6930,0.0097,0.4409,0.0005</t>
-  </si>
-  <si>
-    <t>0.9356,0.0039,0.1161,0.0002</t>
-  </si>
-  <si>
-    <t>0.4918,0.0054,0.7915,0.0001</t>
-  </si>
-  <si>
-    <t>0.3195,0.2305,0.4442,0.0033</t>
-  </si>
-  <si>
-    <t>0.2716,0.0017,0.9004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9371,0.0231,0.0229,0.0033</t>
-  </si>
-  <si>
-    <t>0.6086,0.3728,0.0522,0.0023</t>
-  </si>
-  <si>
-    <t>0.8143,0.0579,0.1151,0.0015</t>
-  </si>
-  <si>
-    <t>0.6712,0.1424,0.2131,0.0027</t>
-  </si>
-  <si>
-    <t>0.0462,0.0118,0.9754,0.0002</t>
-  </si>
-  <si>
-    <t>0.1480,0.0022,0.9351,0.0001</t>
-  </si>
-  <si>
-    <t>0.7281,0.0033,0.5191,0.0003</t>
-  </si>
-  <si>
-    <t>0.7333,0.0025,0.5036,0.0002</t>
-  </si>
-  <si>
-    <t>0.1966,0.0172,0.9062,0.0023</t>
-  </si>
-  <si>
-    <t>0.1388,0.0108,0.9163,0.0003</t>
-  </si>
-  <si>
-    <t>0.9762,0.0084,0.0057,0.0010</t>
-  </si>
-  <si>
-    <t>0.9740,0.0094,0.0102,0.0010</t>
-  </si>
-  <si>
-    <t>0.9780,0.0058,0.0066,0.0018</t>
-  </si>
-  <si>
-    <t>0.7375,0.0163,0.4461,0.0040</t>
-  </si>
-  <si>
-    <t>0.9910,0.0013,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.9843,0.0031,0.0030,0.0015</t>
-  </si>
-  <si>
-    <t>0.9687,0.0172,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.0663,0.0131,0.9657,0.0001</t>
-  </si>
-  <si>
-    <t>0.0247,0.0122,0.9925,0.0001</t>
-  </si>
-  <si>
-    <t>0.7768,0.0105,0.3740,0.0006</t>
-  </si>
-  <si>
-    <t>0.0061,0.1038,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0681,0.0054,0.9768,0.0001</t>
-  </si>
-  <si>
-    <t>0.8582,0.0928,0.0441,0.0011</t>
-  </si>
-  <si>
-    <t>0.1915,0.8325,0.0159,0.0002</t>
-  </si>
-  <si>
-    <t>0.9808,0.0048,0.0149,0.0008</t>
-  </si>
-  <si>
-    <t>0.9861,0.0017,0.0112,0.0007</t>
-  </si>
-  <si>
-    <t>0.4372,0.0270,0.7213,0.0036</t>
-  </si>
-  <si>
-    <t>0.0274,0.4204,0.9014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0735,0.0277,0.9555,0.0001</t>
-  </si>
-  <si>
-    <t>0.0199,0.8641,0.7680,0.0005</t>
-  </si>
-  <si>
-    <t>0.0367,0.7311,0.8205,0.0002</t>
-  </si>
-  <si>
-    <t>0.9415,0.0055,0.0423,0.0042</t>
-  </si>
-  <si>
-    <t>0.9338,0.0115,0.0153,0.0084</t>
-  </si>
-  <si>
-    <t>0.9772,0.0050,0.0045,0.0017</t>
-  </si>
-  <si>
-    <t>0.9743,0.0030,0.0058,0.0043</t>
-  </si>
-  <si>
-    <t>0.9524,0.0064,0.0328,0.0039</t>
-  </si>
-  <si>
-    <t>0.9626,0.0080,0.0050,0.0047</t>
-  </si>
-  <si>
-    <t>0.2404,0.0247,0.8169,0.0004</t>
-  </si>
-  <si>
-    <t>0.1479,0.0060,0.9642,0.0000</t>
-  </si>
-  <si>
-    <t>0.1547,0.0054,0.9309,0.0001</t>
-  </si>
-  <si>
-    <t>0.4290,0.0100,0.7656,0.0005</t>
-  </si>
-  <si>
-    <t>0.0436,0.0507,0.9704,0.0001</t>
-  </si>
-  <si>
-    <t>0.2546,0.1306,0.5753,0.0005</t>
-  </si>
-  <si>
-    <t>0.9792,0.0078,0.0057,0.0013</t>
-  </si>
-  <si>
-    <t>0.9867,0.0028,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.9809,0.0047,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.9813,0.0057,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.9830,0.0051,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.9722,0.0068,0.0081,0.0034</t>
-  </si>
-  <si>
-    <t>0.9907,0.0018,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9871,0.0022,0.0020,0.0011</t>
-  </si>
-  <si>
-    <t>0.9886,0.0014,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.9797,0.0040,0.0025,0.0027</t>
-  </si>
-  <si>
-    <t>0.9711,0.0124,0.0043,0.0022</t>
-  </si>
-  <si>
-    <t>0.9867,0.0018,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9843,0.0025,0.0040,0.0015</t>
-  </si>
-  <si>
-    <t>0.9682,0.0095,0.0062,0.0037</t>
-  </si>
-  <si>
-    <t>0.9730,0.0124,0.0037,0.0015</t>
-  </si>
-  <si>
-    <t>0.9873,0.0009,0.0015,0.0023</t>
-  </si>
-  <si>
-    <t>0.0565,0.0083,0.9683,0.0003</t>
-  </si>
-  <si>
-    <t>0.8693,0.0172,0.1575,0.0007</t>
-  </si>
-  <si>
-    <t>0.9744,0.0022,0.0300,0.0005</t>
-  </si>
-  <si>
-    <t>0.7875,0.0053,0.3857,0.0006</t>
-  </si>
-  <si>
-    <t>0.9037,0.0923,0.0129,0.0016</t>
-  </si>
-  <si>
-    <t>0.9701,0.0174,0.0085,0.0010</t>
-  </si>
-  <si>
-    <t>0.9578,0.0193,0.0143,0.0017</t>
-  </si>
-  <si>
-    <t>0.9623,0.0153,0.0185,0.0009</t>
-  </si>
-  <si>
-    <t>0.9102,0.0684,0.0270,0.0018</t>
-  </si>
-  <si>
-    <t>0.8806,0.0961,0.0208,0.0024</t>
-  </si>
-  <si>
-    <t>0.9558,0.0272,0.0069,0.0016</t>
-  </si>
-  <si>
-    <t>0.9178,0.0247,0.0772,0.0016</t>
-  </si>
-  <si>
-    <t>0.8743,0.0047,0.2431,0.0006</t>
-  </si>
-  <si>
-    <t>0.9729,0.0043,0.0206,0.0004</t>
-  </si>
-  <si>
-    <t>0.9360,0.0096,0.0685,0.0013</t>
-  </si>
-  <si>
-    <t>0.9611,0.0056,0.0281,0.0018</t>
-  </si>
-  <si>
-    <t>0.6164,0.2852,0.0582,0.0016</t>
-  </si>
-  <si>
-    <t>0.5929,0.2825,0.0485,0.0007</t>
-  </si>
-  <si>
-    <t>0.9549,0.0118,0.0315,0.0016</t>
-  </si>
-  <si>
-    <t>0.0594,0.3769,0.8606,0.0021</t>
-  </si>
-  <si>
-    <t>0.9641,0.0161,0.0204,0.0013</t>
-  </si>
-  <si>
-    <t>0.9788,0.0093,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.8151,0.1290,0.0487,0.0065</t>
-  </si>
-  <si>
-    <t>0.9858,0.0026,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.9845,0.0032,0.0059,0.0009</t>
-  </si>
-  <si>
-    <t>0.9651,0.0063,0.0051,0.0076</t>
-  </si>
-  <si>
-    <t>0.9764,0.0047,0.0071,0.0016</t>
-  </si>
-  <si>
-    <t>0.9753,0.0052,0.0031,0.0030</t>
-  </si>
-  <si>
-    <t>0.9809,0.0038,0.0119,0.0012</t>
-  </si>
-  <si>
-    <t>0.9790,0.0048,0.0072,0.0017</t>
-  </si>
-  <si>
-    <t>0.9739,0.0069,0.0047,0.0027</t>
-  </si>
-  <si>
-    <t>0.1264,0.0084,0.9250,0.0004</t>
-  </si>
-  <si>
-    <t>0.2920,0.0115,0.8173,0.0001</t>
-  </si>
-  <si>
-    <t>0.1401,0.0112,0.9356,0.0003</t>
-  </si>
-  <si>
-    <t>0.7896,0.0030,0.4213,0.0001</t>
-  </si>
-  <si>
-    <t>0.9733,0.0062,0.0153,0.0006</t>
-  </si>
-  <si>
-    <t>0.9681,0.0128,0.0110,0.0004</t>
-  </si>
-  <si>
-    <t>0.9542,0.0035,0.0733,0.0009</t>
-  </si>
-  <si>
-    <t>0.9898,0.0017,0.0098,0.0002</t>
-  </si>
-  <si>
-    <t>0.9755,0.0025,0.0066,0.0029</t>
-  </si>
-  <si>
-    <t>0.9199,0.0055,0.0223,0.0201</t>
-  </si>
-  <si>
-    <t>0.9771,0.0022,0.0057,0.0029</t>
-  </si>
-  <si>
-    <t>0.9567,0.0063,0.0211,0.0036</t>
-  </si>
-  <si>
-    <t>0.0074,0.8454,0.9541,0.0004</t>
-  </si>
-  <si>
-    <t>0.9697,0.0067,0.0049,0.0026</t>
-  </si>
-  <si>
-    <t>0.9586,0.0161,0.0129,0.0021</t>
-  </si>
-  <si>
-    <t>0.9855,0.0035,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.9776,0.0101,0.0054,0.0008</t>
-  </si>
-  <si>
-    <t>0.9786,0.0068,0.0055,0.0011</t>
-  </si>
-  <si>
-    <t>0.9807,0.0034,0.0110,0.0007</t>
-  </si>
-  <si>
-    <t>0.9777,0.0039,0.0059,0.0019</t>
-  </si>
-  <si>
-    <t>0.0967,0.0794,0.9029,0.0203</t>
-  </si>
-  <si>
-    <t>0.9891,0.0006,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.9739,0.0079,0.0066,0.0014</t>
-  </si>
-  <si>
-    <t>0.9197,0.0246,0.0586,0.0033</t>
-  </si>
-  <si>
-    <t>0.9697,0.0086,0.0180,0.0011</t>
-  </si>
-  <si>
-    <t>0.9445,0.0167,0.0252,0.0024</t>
-  </si>
-  <si>
-    <t>0.9714,0.0103,0.0107,0.0010</t>
-  </si>
-  <si>
-    <t>0.9470,0.0177,0.0287,0.0010</t>
-  </si>
-  <si>
-    <t>0.9814,0.0049,0.0095,0.0005</t>
-  </si>
-  <si>
-    <t>0.9789,0.0063,0.0031,0.0017</t>
-  </si>
-  <si>
-    <t>0.9680,0.0170,0.0059,0.0016</t>
-  </si>
-  <si>
-    <t>0.9804,0.0062,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.9827,0.0035,0.0038,0.0022</t>
-  </si>
-  <si>
-    <t>0.9784,0.0039,0.0057,0.0020</t>
-  </si>
-  <si>
-    <t>0.9835,0.0024,0.0040,0.0018</t>
-  </si>
-  <si>
-    <t>0.9767,0.0037,0.0053,0.0027</t>
-  </si>
-  <si>
-    <t>0.9539,0.0149,0.0044,0.0051</t>
-  </si>
-  <si>
-    <t>0.9672,0.0143,0.0050,0.0013</t>
-  </si>
-  <si>
-    <t>0.9579,0.0126,0.0104,0.0030</t>
-  </si>
-  <si>
-    <t>0.9634,0.0176,0.0082,0.0014</t>
-  </si>
-  <si>
-    <t>0.9695,0.0099,0.0150,0.0015</t>
-  </si>
-  <si>
-    <t>0.9842,0.0025,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.9683,0.0063,0.0105,0.0029</t>
-  </si>
-  <si>
-    <t>0.9714,0.0090,0.0070,0.0015</t>
-  </si>
-  <si>
-    <t>0.9511,0.0177,0.0235,0.0017</t>
-  </si>
-  <si>
-    <t>0.0915,0.0149,0.9638,0.0006</t>
-  </si>
-  <si>
-    <t>0.9790,0.0031,0.0061,0.0021</t>
-  </si>
-  <si>
-    <t>0.1291,0.0047,0.9494,0.0003</t>
-  </si>
-  <si>
-    <t>0.4697,0.0042,0.8016,0.0004</t>
-  </si>
-  <si>
-    <t>0.8788,0.0130,0.1866,0.0030</t>
-  </si>
-  <si>
-    <t>0.4975,0.0107,0.7266,0.0003</t>
-  </si>
-  <si>
-    <t>0.4298,0.0076,0.7675,0.0004</t>
-  </si>
-  <si>
-    <t>0.5091,0.0034,0.7228,0.0001</t>
-  </si>
-  <si>
-    <t>0.2265,0.0068,0.8796,0.0004</t>
-  </si>
-  <si>
-    <t>0.9561,0.0058,0.0570,0.0006</t>
-  </si>
-  <si>
-    <t>0.9402,0.0048,0.0898,0.0009</t>
-  </si>
-  <si>
-    <t>0.9810,0.0050,0.0144,0.0006</t>
-  </si>
-  <si>
-    <t>0.9535,0.0050,0.0514,0.0004</t>
-  </si>
-  <si>
-    <t>0.8546,0.0211,0.1873,0.0029</t>
-  </si>
-  <si>
-    <t>0.9561,0.0073,0.0498,0.0006</t>
-  </si>
-  <si>
-    <t>0.9120,0.0171,0.0760,0.0025</t>
-  </si>
-  <si>
-    <t>0.9861,0.0016,0.0179,0.0002</t>
-  </si>
-  <si>
-    <t>0.9850,0.0052,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9606,0.0227,0.0106,0.0011</t>
-  </si>
-  <si>
-    <t>0.9802,0.0075,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.9794,0.0071,0.0089,0.0011</t>
-  </si>
-  <si>
-    <t>0.9737,0.0045,0.0043,0.0028</t>
-  </si>
-  <si>
-    <t>0.9650,0.0058,0.0339,0.0004</t>
-  </si>
-  <si>
-    <t>0.9059,0.0096,0.1324,0.0021</t>
-  </si>
-  <si>
-    <t>0.9289,0.0063,0.0938,0.0014</t>
-  </si>
-  <si>
-    <t>0.8794,0.0042,0.2581,0.0006</t>
-  </si>
-  <si>
-    <t>0.9759,0.0063,0.0178,0.0005</t>
-  </si>
-  <si>
-    <t>0.6499,0.0116,0.5031,0.0022</t>
-  </si>
-  <si>
-    <t>0.8775,0.0047,0.2819,0.0002</t>
-  </si>
-  <si>
-    <t>0.4556,0.0052,0.7948,0.0001</t>
-  </si>
-  <si>
-    <t>0.9411,0.0033,0.1369,0.0002</t>
-  </si>
-  <si>
-    <t>0.8147,0.0110,0.2869,0.0003</t>
-  </si>
-  <si>
-    <t>0.9866,0.0024,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.9903,0.0034,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9684,0.0117,0.0079,0.0029</t>
-  </si>
-  <si>
-    <t>0.9845,0.0043,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.9828,0.0037,0.0025,0.0018</t>
-  </si>
-  <si>
-    <t>0.9818,0.0055,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.9877,0.0039,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9804,0.0050,0.0040,0.0017</t>
-  </si>
-  <si>
-    <t>0.8785,0.0236,0.1674,0.0057</t>
-  </si>
-  <si>
-    <t>0.9338,0.0146,0.0554,0.0026</t>
-  </si>
-  <si>
-    <t>0.9710,0.0084,0.0133,0.0014</t>
-  </si>
-  <si>
-    <t>0.1654,0.0043,0.9025,0.0002</t>
-  </si>
-  <si>
-    <t>0.0540,0.0079,0.9807,0.0004</t>
-  </si>
-  <si>
-    <t>0.7869,0.0072,0.3903,0.0003</t>
-  </si>
-  <si>
-    <t>0.1296,0.0019,0.9548,0.0001</t>
-  </si>
-  <si>
-    <t>0.7476,0.0032,0.5260,0.0002</t>
-  </si>
-  <si>
-    <t>0.0167,0.0020,0.9919,0.0003</t>
-  </si>
-  <si>
-    <t>0.7378,0.0132,0.3529,0.0016</t>
-  </si>
-  <si>
-    <t>0.6481,0.0147,0.4930,0.0019</t>
-  </si>
-  <si>
-    <t>0.9435,0.0051,0.0807,0.0009</t>
-  </si>
-  <si>
-    <t>0.9746,0.0031,0.0375,0.0006</t>
-  </si>
-  <si>
-    <t>0.9448,0.0061,0.0767,0.0007</t>
-  </si>
-  <si>
-    <t>0.9901,0.0025,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9763,0.0098,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.9733,0.0059,0.0090,0.0020</t>
-  </si>
-  <si>
-    <t>0.9679,0.0111,0.0086,0.0025</t>
-  </si>
-  <si>
-    <t>0.9755,0.0074,0.0059,0.0018</t>
-  </si>
-  <si>
-    <t>0.9909,0.0017,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9892,0.0014,0.0051,0.0011</t>
-  </si>
-  <si>
-    <t>0.9897,0.0013,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.7932,0.0148,0.2559,0.0004</t>
-  </si>
-  <si>
-    <t>0.1043,0.0368,0.9283,0.0006</t>
-  </si>
-  <si>
-    <t>0.1436,0.0047,0.9503,0.0001</t>
-  </si>
-  <si>
-    <t>0.7790,0.0046,0.3295,0.0002</t>
-  </si>
-  <si>
-    <t>0.6596,0.0019,0.6005,0.0002</t>
-  </si>
-  <si>
-    <t>0.8326,0.0169,0.2585,0.0039</t>
-  </si>
-  <si>
-    <t>0.9661,0.0030,0.0538,0.0002</t>
-  </si>
-  <si>
-    <t>0.4303,0.0055,0.7601,0.0013</t>
-  </si>
-  <si>
-    <t>0.9849,0.0014,0.0073,0.0009</t>
-  </si>
-  <si>
-    <t>0.9510,0.0052,0.0345,0.0047</t>
-  </si>
-  <si>
-    <t>0.9246,0.0251,0.0333,0.0087</t>
-  </si>
-  <si>
-    <t>0.9378,0.0068,0.0144,0.0134</t>
-  </si>
-  <si>
-    <t>0.9282,0.0035,0.0145,0.0221</t>
-  </si>
-  <si>
-    <t>0.9802,0.0053,0.0059,0.0006</t>
+    <t>0.9299,0.0290,0.0285,0.0020</t>
+  </si>
+  <si>
+    <t>0.9653,0.0052,0.0067,0.0033</t>
+  </si>
+  <si>
+    <t>0.9506,0.0219,0.0134,0.0020</t>
+  </si>
+  <si>
+    <t>0.9751,0.0049,0.0035,0.0019</t>
+  </si>
+  <si>
+    <t>0.9798,0.0077,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.9778,0.0056,0.0031,0.0023</t>
+  </si>
+  <si>
+    <t>0.9743,0.0058,0.0064,0.0022</t>
+  </si>
+  <si>
+    <t>0.9717,0.0086,0.0072,0.0026</t>
+  </si>
+  <si>
+    <t>0.9811,0.0032,0.0028,0.0025</t>
+  </si>
+  <si>
+    <t>0.9877,0.0051,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.9809,0.0040,0.0044,0.0015</t>
+  </si>
+  <si>
+    <t>0.9755,0.0085,0.0046,0.0013</t>
+  </si>
+  <si>
+    <t>0.9565,0.0046,0.0737,0.0006</t>
+  </si>
+  <si>
+    <t>0.8311,0.0173,0.2250,0.0010</t>
+  </si>
+  <si>
+    <t>0.9791,0.0025,0.0300,0.0002</t>
+  </si>
+  <si>
+    <t>0.9546,0.0090,0.0573,0.0007</t>
+  </si>
+  <si>
+    <t>0.9793,0.0042,0.0242,0.0003</t>
+  </si>
+  <si>
+    <t>0.9247,0.0639,0.0162,0.0013</t>
+  </si>
+  <si>
+    <t>0.9740,0.0135,0.0110,0.0008</t>
+  </si>
+  <si>
+    <t>0.9590,0.0213,0.0118,0.0016</t>
+  </si>
+  <si>
+    <t>0.9456,0.0264,0.0227,0.0015</t>
+  </si>
+  <si>
+    <t>0.8417,0.1495,0.0389,0.0030</t>
+  </si>
+  <si>
+    <t>0.9800,0.0017,0.0294,0.0003</t>
+  </si>
+  <si>
+    <t>0.9337,0.0063,0.1054,0.0007</t>
+  </si>
+  <si>
+    <t>0.8064,0.0048,0.3440,0.0003</t>
+  </si>
+  <si>
+    <t>0.9630,0.0015,0.0662,0.0003</t>
+  </si>
+  <si>
+    <t>0.9654,0.0010,0.0738,0.0003</t>
+  </si>
+  <si>
+    <t>0.9573,0.0032,0.0747,0.0006</t>
+  </si>
+  <si>
+    <t>0.5387,0.0228,0.4647,0.0010</t>
+  </si>
+  <si>
+    <t>0.9708,0.0109,0.0123,0.0007</t>
+  </si>
+  <si>
+    <t>0.9245,0.0406,0.0233,0.0011</t>
+  </si>
+  <si>
+    <t>0.0302,0.0265,0.9744,0.0037</t>
+  </si>
+  <si>
+    <t>0.9580,0.0122,0.0293,0.0010</t>
+  </si>
+  <si>
+    <t>0.9610,0.0201,0.0149,0.0010</t>
+  </si>
+  <si>
+    <t>0.8061,0.0352,0.1577,0.0008</t>
+  </si>
+  <si>
+    <t>0.8624,0.1091,0.0403,0.0029</t>
+  </si>
+  <si>
+    <t>0.9088,0.0641,0.0371,0.0031</t>
+  </si>
+  <si>
+    <t>0.3602,0.0080,0.8261,0.0004</t>
+  </si>
+  <si>
+    <t>0.1994,0.0060,0.8858,0.0008</t>
+  </si>
+  <si>
+    <t>0.5116,0.0069,0.6657,0.0003</t>
+  </si>
+  <si>
+    <t>0.9636,0.0009,0.1057,0.0003</t>
+  </si>
+  <si>
+    <t>0.5023,0.0038,0.7164,0.0002</t>
+  </si>
+  <si>
+    <t>0.3489,0.0174,0.7443,0.0006</t>
+  </si>
+  <si>
+    <t>0.0512,0.0082,0.9743,0.0007</t>
+  </si>
+  <si>
+    <t>0.9571,0.0165,0.0091,0.0022</t>
+  </si>
+  <si>
+    <t>0.5454,0.3394,0.1171,0.0065</t>
+  </si>
+  <si>
+    <t>0.4828,0.1472,0.2733,0.0028</t>
+  </si>
+  <si>
+    <t>0.6094,0.3200,0.0707,0.0015</t>
+  </si>
+  <si>
+    <t>0.0355,0.0039,0.9805,0.0002</t>
+  </si>
+  <si>
+    <t>0.1668,0.0313,0.8864,0.0002</t>
+  </si>
+  <si>
+    <t>0.9244,0.0032,0.1665,0.0003</t>
+  </si>
+  <si>
+    <t>0.7833,0.0030,0.4356,0.0002</t>
+  </si>
+  <si>
+    <t>0.2355,0.0086,0.9218,0.0005</t>
+  </si>
+  <si>
+    <t>0.7850,0.0040,0.4513,0.0002</t>
+  </si>
+  <si>
+    <t>0.9860,0.0034,0.0042,0.0008</t>
+  </si>
+  <si>
+    <t>0.9677,0.0092,0.0079,0.0029</t>
+  </si>
+  <si>
+    <t>0.9738,0.0097,0.0047,0.0018</t>
+  </si>
+  <si>
+    <t>0.4899,0.0304,0.6738,0.0044</t>
+  </si>
+  <si>
+    <t>0.9719,0.0068,0.0064,0.0026</t>
+  </si>
+  <si>
+    <t>0.9745,0.0058,0.0026,0.0030</t>
+  </si>
+  <si>
+    <t>0.9731,0.0085,0.0065,0.0016</t>
+  </si>
+  <si>
+    <t>0.2589,0.0773,0.8143,0.0004</t>
+  </si>
+  <si>
+    <t>0.1625,0.0059,0.9299,0.0004</t>
+  </si>
+  <si>
+    <t>0.2773,0.0211,0.8131,0.0004</t>
+  </si>
+  <si>
+    <t>0.0731,0.3421,0.8274,0.0002</t>
+  </si>
+  <si>
+    <t>0.0102,0.0039,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.8498,0.0919,0.0180,0.0002</t>
+  </si>
+  <si>
+    <t>0.2126,0.8185,0.0271,0.0002</t>
+  </si>
+  <si>
+    <t>0.9758,0.0053,0.0118,0.0007</t>
+  </si>
+  <si>
+    <t>0.9738,0.0067,0.0173,0.0009</t>
+  </si>
+  <si>
+    <t>0.0439,0.0221,0.9739,0.0014</t>
+  </si>
+  <si>
+    <t>0.2697,0.0668,0.7950,0.0001</t>
+  </si>
+  <si>
+    <t>0.1091,0.2945,0.7365,0.0006</t>
+  </si>
+  <si>
+    <t>0.1190,0.5314,0.5282,0.0002</t>
+  </si>
+  <si>
+    <t>0.2133,0.0717,0.8329,0.0003</t>
+  </si>
+  <si>
+    <t>0.9693,0.0036,0.0118,0.0028</t>
+  </si>
+  <si>
+    <t>0.9735,0.0036,0.0048,0.0024</t>
+  </si>
+  <si>
+    <t>0.9688,0.0049,0.0079,0.0028</t>
+  </si>
+  <si>
+    <t>0.9440,0.0041,0.0116,0.0171</t>
+  </si>
+  <si>
+    <t>0.9568,0.0111,0.0192,0.0038</t>
+  </si>
+  <si>
+    <t>0.9537,0.0054,0.0122,0.0103</t>
+  </si>
+  <si>
+    <t>0.2161,0.1077,0.8152,0.0003</t>
+  </si>
+  <si>
+    <t>0.0928,0.0314,0.9501,0.0003</t>
+  </si>
+  <si>
+    <t>0.4028,0.0062,0.8211,0.0001</t>
+  </si>
+  <si>
+    <t>0.2666,0.0284,0.8501,0.0007</t>
+  </si>
+  <si>
+    <t>0.1578,0.1233,0.8196,0.0002</t>
+  </si>
+  <si>
+    <t>0.3250,0.0584,0.6431,0.0006</t>
+  </si>
+  <si>
+    <t>0.9925,0.0019,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9812,0.0067,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.9852,0.0037,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.9695,0.0105,0.0054,0.0019</t>
+  </si>
+  <si>
+    <t>0.9724,0.0075,0.0035,0.0027</t>
+  </si>
+  <si>
+    <t>0.9641,0.0168,0.0054,0.0029</t>
+  </si>
+  <si>
+    <t>0.9841,0.0032,0.0042,0.0014</t>
+  </si>
+  <si>
+    <t>0.9906,0.0019,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9525,0.0117,0.0082,0.0095</t>
+  </si>
+  <si>
+    <t>0.9913,0.0020,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9887,0.0018,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.9801,0.0041,0.0036,0.0022</t>
+  </si>
+  <si>
+    <t>0.9847,0.0013,0.0026,0.0028</t>
+  </si>
+  <si>
+    <t>0.9621,0.0138,0.0073,0.0029</t>
+  </si>
+  <si>
+    <t>0.9842,0.0038,0.0048,0.0014</t>
+  </si>
+  <si>
+    <t>0.9771,0.0062,0.0038,0.0021</t>
+  </si>
+  <si>
+    <t>0.4836,0.0057,0.6559,0.0004</t>
+  </si>
+  <si>
+    <t>0.5924,0.0044,0.6391,0.0004</t>
+  </si>
+  <si>
+    <t>0.9784,0.0033,0.0222,0.0003</t>
+  </si>
+  <si>
+    <t>0.8514,0.0085,0.2283,0.0005</t>
+  </si>
+  <si>
+    <t>0.9071,0.0628,0.0281,0.0027</t>
+  </si>
+  <si>
+    <t>0.9476,0.0387,0.0122,0.0007</t>
+  </si>
+  <si>
+    <t>0.9522,0.0278,0.0097,0.0016</t>
+  </si>
+  <si>
+    <t>0.9116,0.0583,0.0153,0.0033</t>
+  </si>
+  <si>
+    <t>0.8424,0.1091,0.0385,0.0012</t>
+  </si>
+  <si>
+    <t>0.8572,0.1657,0.0166,0.0017</t>
+  </si>
+  <si>
+    <t>0.9611,0.0192,0.0090,0.0017</t>
+  </si>
+  <si>
+    <t>0.9709,0.0075,0.0119,0.0009</t>
+  </si>
+  <si>
+    <t>0.5697,0.0168,0.5838,0.0017</t>
+  </si>
+  <si>
+    <t>0.9399,0.0234,0.0295,0.0013</t>
+  </si>
+  <si>
+    <t>0.9055,0.0048,0.1693,0.0014</t>
+  </si>
+  <si>
+    <t>0.9624,0.0047,0.0208,0.0030</t>
+  </si>
+  <si>
+    <t>0.3073,0.5382,0.1806,0.0029</t>
+  </si>
+  <si>
+    <t>0.3398,0.5852,0.0483,0.0007</t>
+  </si>
+  <si>
+    <t>0.9774,0.0024,0.0208,0.0007</t>
+  </si>
+  <si>
+    <t>0.0476,0.3055,0.9103,0.0010</t>
+  </si>
+  <si>
+    <t>0.9714,0.0143,0.0122,0.0006</t>
+  </si>
+  <si>
+    <t>0.9648,0.0107,0.0179,0.0018</t>
+  </si>
+  <si>
+    <t>0.9642,0.0139,0.0108,0.0013</t>
+  </si>
+  <si>
+    <t>0.9807,0.0056,0.0074,0.0011</t>
+  </si>
+  <si>
+    <t>0.9858,0.0022,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9817,0.0030,0.0040,0.0021</t>
+  </si>
+  <si>
+    <t>0.9721,0.0067,0.0072,0.0021</t>
+  </si>
+  <si>
+    <t>0.9852,0.0030,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.9536,0.0183,0.0272,0.0025</t>
+  </si>
+  <si>
+    <t>0.9717,0.0076,0.0049,0.0025</t>
+  </si>
+  <si>
+    <t>0.9828,0.0055,0.0073,0.0008</t>
+  </si>
+  <si>
+    <t>0.0557,0.0184,0.9543,0.0003</t>
+  </si>
+  <si>
+    <t>0.3425,0.0032,0.8799,0.0001</t>
+  </si>
+  <si>
+    <t>0.2219,0.0127,0.8933,0.0003</t>
+  </si>
+  <si>
+    <t>0.6541,0.0033,0.5836,0.0002</t>
+  </si>
+  <si>
+    <t>0.9891,0.0011,0.0087,0.0002</t>
+  </si>
+  <si>
+    <t>0.9407,0.0130,0.0578,0.0028</t>
+  </si>
+  <si>
+    <t>0.8754,0.0085,0.2236,0.0010</t>
+  </si>
+  <si>
+    <t>0.9703,0.0082,0.0181,0.0006</t>
+  </si>
+  <si>
+    <t>0.9845,0.0031,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.8455,0.0190,0.0952,0.0316</t>
+  </si>
+  <si>
+    <t>0.9726,0.0022,0.0088,0.0046</t>
+  </si>
+  <si>
+    <t>0.9509,0.0047,0.0412,0.0050</t>
+  </si>
+  <si>
+    <t>0.0110,0.5667,0.9583,0.0001</t>
+  </si>
+  <si>
+    <t>0.9705,0.0090,0.0060,0.0028</t>
+  </si>
+  <si>
+    <t>0.9654,0.0148,0.0097,0.0010</t>
+  </si>
+  <si>
+    <t>0.9823,0.0038,0.0057,0.0012</t>
+  </si>
+  <si>
+    <t>0.9862,0.0043,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.9853,0.0038,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.9796,0.0037,0.0076,0.0016</t>
+  </si>
+  <si>
+    <t>0.9809,0.0070,0.0098,0.0007</t>
+  </si>
+  <si>
+    <t>0.0481,0.0765,0.9533,0.0071</t>
+  </si>
+  <si>
+    <t>0.9818,0.0044,0.0069,0.0007</t>
+  </si>
+  <si>
+    <t>0.9762,0.0056,0.0080,0.0014</t>
+  </si>
+  <si>
+    <t>0.9171,0.0562,0.0190,0.0014</t>
+  </si>
+  <si>
+    <t>0.9723,0.0122,0.0066,0.0005</t>
+  </si>
+  <si>
+    <t>0.9806,0.0036,0.0109,0.0006</t>
+  </si>
+  <si>
+    <t>0.9872,0.0038,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.9883,0.0022,0.0058,0.0004</t>
+  </si>
+  <si>
+    <t>0.9712,0.0097,0.0117,0.0010</t>
+  </si>
+  <si>
+    <t>0.9575,0.0160,0.0054,0.0035</t>
+  </si>
+  <si>
+    <t>0.9614,0.0137,0.0097,0.0029</t>
+  </si>
+  <si>
+    <t>0.9728,0.0046,0.0069,0.0027</t>
+  </si>
+  <si>
+    <t>0.9862,0.0018,0.0020,0.0023</t>
+  </si>
+  <si>
+    <t>0.9829,0.0043,0.0042,0.0011</t>
+  </si>
+  <si>
+    <t>0.9785,0.0078,0.0032,0.0011</t>
+  </si>
+  <si>
+    <t>0.9812,0.0033,0.0067,0.0015</t>
+  </si>
+  <si>
+    <t>0.9920,0.0018,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.8961,0.0768,0.0142,0.0034</t>
+  </si>
+  <si>
+    <t>0.9420,0.0235,0.0257,0.0028</t>
+  </si>
+  <si>
+    <t>0.8920,0.0705,0.0345,0.0059</t>
+  </si>
+  <si>
+    <t>0.9097,0.0286,0.0748,0.0096</t>
+  </si>
+  <si>
+    <t>0.9922,0.0019,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9881,0.0022,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9840,0.0039,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.9696,0.0147,0.0076,0.0012</t>
+  </si>
+  <si>
+    <t>0.0169,0.0142,0.9904,0.0004</t>
+  </si>
+  <si>
+    <t>0.9915,0.0017,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.4959,0.0017,0.7753,0.0002</t>
+  </si>
+  <si>
+    <t>0.7147,0.0095,0.4950,0.0006</t>
+  </si>
+  <si>
+    <t>0.8858,0.0090,0.1656,0.0011</t>
+  </si>
+  <si>
+    <t>0.2230,0.0033,0.9044,0.0002</t>
+  </si>
+  <si>
+    <t>0.5940,0.0079,0.6689,0.0006</t>
+  </si>
+  <si>
+    <t>0.2959,0.0022,0.8810,0.0002</t>
+  </si>
+  <si>
+    <t>0.4534,0.0090,0.6678,0.0005</t>
+  </si>
+  <si>
+    <t>0.8780,0.0137,0.1605,0.0016</t>
+  </si>
+  <si>
+    <t>0.9397,0.0137,0.0433,0.0016</t>
+  </si>
+  <si>
+    <t>0.8071,0.0239,0.2795,0.0030</t>
+  </si>
+  <si>
+    <t>0.9355,0.0060,0.0986,0.0005</t>
+  </si>
+  <si>
+    <t>0.9308,0.0084,0.0905,0.0007</t>
+  </si>
+  <si>
+    <t>0.9553,0.0068,0.0471,0.0005</t>
+  </si>
+  <si>
+    <t>0.8597,0.0209,0.1604,0.0044</t>
+  </si>
+  <si>
+    <t>0.9232,0.0122,0.1006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9892,0.0046,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9736,0.0112,0.0085,0.0013</t>
+  </si>
+  <si>
+    <t>0.9709,0.0165,0.0089,0.0009</t>
+  </si>
+  <si>
+    <t>0.9875,0.0047,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.9891,0.0027,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.9467,0.0075,0.0642,0.0005</t>
+  </si>
+  <si>
+    <t>0.9893,0.0010,0.0151,0.0002</t>
+  </si>
+  <si>
+    <t>0.9557,0.0053,0.0525,0.0004</t>
+  </si>
+  <si>
+    <t>0.8528,0.0139,0.2094,0.0010</t>
+  </si>
+  <si>
+    <t>0.9427,0.0145,0.0385,0.0019</t>
+  </si>
+  <si>
+    <t>0.8537,0.0062,0.2448,0.0008</t>
+  </si>
+  <si>
+    <t>0.6807,0.0051,0.5526,0.0001</t>
+  </si>
+  <si>
+    <t>0.6245,0.0065,0.7310,0.0001</t>
+  </si>
+  <si>
+    <t>0.6853,0.0014,0.6537,0.0001</t>
+  </si>
+  <si>
+    <t>0.7649,0.0124,0.3616,0.0003</t>
+  </si>
+  <si>
+    <t>0.9871,0.0027,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9880,0.0034,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.9859,0.0031,0.0108,0.0008</t>
+  </si>
+  <si>
+    <t>0.9902,0.0023,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.9888,0.0029,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9860,0.0035,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.9790,0.0065,0.0036,0.0018</t>
+  </si>
+  <si>
+    <t>0.9858,0.0021,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9400,0.0138,0.0549,0.0019</t>
+  </si>
+  <si>
+    <t>0.9189,0.0175,0.0642,0.0014</t>
+  </si>
+  <si>
+    <t>0.9801,0.0064,0.0046,0.0007</t>
+  </si>
+  <si>
+    <t>0.5447,0.0050,0.7434,0.0002</t>
+  </si>
+  <si>
+    <t>0.0137,0.0065,0.9922,0.0006</t>
+  </si>
+  <si>
+    <t>0.7398,0.0166,0.3254,0.0008</t>
+  </si>
+  <si>
+    <t>0.0470,0.0020,0.9860,0.0001</t>
+  </si>
+  <si>
+    <t>0.8859,0.0031,0.2732,0.0003</t>
+  </si>
+  <si>
+    <t>0.0213,0.0128,0.9912,0.0002</t>
+  </si>
+  <si>
+    <t>0.1932,0.0069,0.8766,0.0008</t>
+  </si>
+  <si>
+    <t>0.9530,0.0084,0.0597,0.0013</t>
+  </si>
+  <si>
+    <t>0.9583,0.0048,0.0671,0.0006</t>
+  </si>
+  <si>
+    <t>0.9373,0.0031,0.1172,0.0005</t>
+  </si>
+  <si>
+    <t>0.9421,0.0045,0.0919,0.0008</t>
+  </si>
+  <si>
+    <t>0.9639,0.0110,0.0072,0.0047</t>
+  </si>
+  <si>
+    <t>0.9845,0.0049,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.9884,0.0023,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9731,0.0105,0.0056,0.0013</t>
+  </si>
+  <si>
+    <t>0.9936,0.0010,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9759,0.0082,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.9789,0.0049,0.0120,0.0012</t>
+  </si>
+  <si>
+    <t>0.9803,0.0053,0.0073,0.0016</t>
+  </si>
+  <si>
+    <t>0.8126,0.0040,0.3459,0.0002</t>
+  </si>
+  <si>
+    <t>0.6310,0.0253,0.3299,0.0003</t>
+  </si>
+  <si>
+    <t>0.0961,0.0140,0.9455,0.0002</t>
+  </si>
+  <si>
+    <t>0.7325,0.0175,0.3851,0.0009</t>
+  </si>
+  <si>
+    <t>0.3954,0.0093,0.7489,0.0003</t>
+  </si>
+  <si>
+    <t>0.9360,0.0107,0.0726,0.0010</t>
+  </si>
+  <si>
+    <t>0.9022,0.0113,0.1174,0.0015</t>
+  </si>
+  <si>
+    <t>0.7752,0.0034,0.4261,0.0006</t>
+  </si>
+  <si>
+    <t>0.9631,0.0048,0.0119,0.0037</t>
+  </si>
+  <si>
+    <t>0.9665,0.0028,0.0412,0.0018</t>
+  </si>
+  <si>
+    <t>0.9828,0.0018,0.0042,0.0021</t>
+  </si>
+  <si>
+    <t>0.8775,0.0096,0.0193,0.0519</t>
+  </si>
+  <si>
+    <t>0.9534,0.0025,0.0052,0.0148</t>
+  </si>
+  <si>
+    <t>0.9833,0.0033,0.0082,0.0005</t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
